--- a/Assets/Data/Excel/SubWaveSpawnConfig.xlsx
+++ b/Assets/Data/Excel/SubWaveSpawnConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F680A5-CA0B-48B2-B688-03DB9FDDB886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43111D27-09B2-4AB8-95B5-6F642C53DFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18210" yWindow="4290" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30690" yWindow="6720" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="13.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -500,7 +500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -546,7 +546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -589,6 +589,75 @@
         <v>0.4</v>
       </c>
       <c r="G7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>102</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>102</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>102</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Excel/SubWaveSpawnConfig.xlsx
+++ b/Assets/Data/Excel/SubWaveSpawnConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43111D27-09B2-4AB8-95B5-6F642C53DFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B84A8-2F7D-4924-A9B8-A123D996BE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30690" yWindow="6720" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="5055" windowWidth="13380" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="13.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -661,6 +661,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>103</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>103</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
